--- a/01데이터베이스/JOIN_Example.xlsx
+++ b/01데이터베이스/JOIN_Example.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11340" tabRatio="500" activeTab="4"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28548" windowHeight="13152" tabRatio="500" activeTab="2"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Inner" sheetId="1" r:id="rId4"/>
@@ -23,27 +23,54 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="18">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="21">
+  <x:si>
+    <x:t>left join</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cumings, Mrs. John Bradley (Florence Briggs Thayer)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Futrelle, Mrs. Jacques Heath (Lily May Peel)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Allen, Mr. William Henry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Survived</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PassengerId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INNER JOIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P_info 테이블</x:t>
+  </x:si>
   <x:si>
     <x:t>Sibsp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NULL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>female</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Parch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>male</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
   </x:si>
   <x:si>
     <x:t>Survived 테이블</x:t>
   </x:si>
   <x:si>
     <x:t>Age</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NULL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INNER JOIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Parch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Survived</x:t>
   </x:si>
   <x:si>
     <x:t>Sex</x:t>
@@ -55,28 +82,10 @@
     <x:t>Heikkinen, Miss. Laina</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
+    <x:t>null</x:t>
   </x:si>
   <x:si>
-    <x:t>Cumings, Mrs. John Bradley (Florence Briggs Thayer)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Futrelle, Mrs. Jacques Heath (Lily May Peel)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Allen, Mr. William Henry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>male</x:t>
-  </x:si>
-  <x:si>
-    <x:t>female</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PassengerId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P_info 테이블</x:t>
+    <x:t>right join</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -176,7 +185,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -219,22 +228,6 @@
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
@@ -269,6 +262,35 @@
     </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="bottom"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+          <x:alignment horizontal="center" vertical="bottom"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="bottom"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
@@ -276,19 +298,6 @@
       </mc:Choice>
       <mc:Fallback>
         <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-          <x:alignment horizontal="center" vertical="bottom"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="bottom"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
           <x:alignment horizontal="center" vertical="bottom"/>
         </x:xf>
       </mc:Fallback>
@@ -319,16 +328,29 @@
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="bottom"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="bottom"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
   </x:cellXfs>
   <x:cellStyles count="3">
     <x:cellStyle name="Normal" xfId="0" builtinId="0" iLevel="0"/>
-    <x:cellStyle name="표준" xfId="2" builtinId="0" iLevel="0"/>
+    <x:cellStyle name="표준" xfId="2"/>
   </x:cellStyles>
   <x:dxfs count="12">
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -998,43 +1020,43 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:11" ht="44.25" customHeight="1">
-      <x:c r="A1" s="5" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
-      <x:c r="J1" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1" s="10"/>
+      <x:c r="A1" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B1" s="10"/>
+      <x:c r="C1" s="10"/>
+      <x:c r="D1" s="10"/>
+      <x:c r="E1" s="10"/>
+      <x:c r="F1" s="10"/>
+      <x:c r="J1" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K1" s="11"/>
     </x:row>
     <x:row r="2" spans="1:11">
       <x:c r="A2" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J2" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J2" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
@@ -1042,10 +1064,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D3" s="2">
         <x:v>22</x:v>
@@ -1056,7 +1078,7 @@
       <x:c r="F3" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J3" s="7">
+      <x:c r="J3" s="5">
         <x:v>2</x:v>
       </x:c>
       <x:c r="K3" s="1">
@@ -1064,14 +1086,14 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
-      <x:c r="A4" s="6">
+      <x:c r="A4" s="4">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D4" s="2">
         <x:v>38</x:v>
@@ -1082,7 +1104,7 @@
       <x:c r="F4" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J4" s="7">
+      <x:c r="J4" s="5">
         <x:v>4</x:v>
       </x:c>
       <x:c r="K4" s="1">
@@ -1094,10 +1116,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D5" s="2">
         <x:v>26</x:v>
@@ -1116,14 +1138,14 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
-      <x:c r="A6" s="6">
+      <x:c r="A6" s="4">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="2">
         <x:v>35</x:v>
@@ -1146,10 +1168,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D7" s="2">
         <x:v>35</x:v>
@@ -1212,20 +1234,20 @@
       <x:c r="K13" s="1"/>
     </x:row>
     <x:row r="14" spans="1:8">
-      <x:c r="A14" s="5" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B14" s="5"/>
-      <x:c r="C14" s="5"/>
-      <x:c r="D14" s="5"/>
-      <x:c r="E14" s="5"/>
-      <x:c r="F14" s="5"/>
-      <x:c r="G14" s="5"/>
-      <x:c r="H14" s="5"/>
+      <x:c r="A14" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B14" s="10"/>
+      <x:c r="C14" s="10"/>
+      <x:c r="D14" s="10"/>
+      <x:c r="E14" s="10"/>
+      <x:c r="F14" s="10"/>
+      <x:c r="G14" s="10"/>
+      <x:c r="H14" s="10"/>
     </x:row>
     <x:row r="15" spans="1:8">
       <x:c r="A15" s="12" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B15" s="12"/>
       <x:c r="C15" s="12"/>
@@ -1233,19 +1255,19 @@
       <x:c r="E15" s="12"/>
       <x:c r="F15" s="12"/>
       <x:c r="G15" s="13" t="s">
-        <x:v>1</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H15" s="13"/>
     </x:row>
     <x:row r="16" spans="1:8">
-      <x:c r="A16" s="6">
+      <x:c r="A16" s="4">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C16" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D16" s="2">
         <x:v>38</x:v>
@@ -1256,7 +1278,7 @@
       <x:c r="F16" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="11">
+      <x:c r="G16" s="8">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H16" s="3">
@@ -1264,14 +1286,14 @@
       </x:c>
     </x:row>
     <x:row r="17" spans="1:8">
-      <x:c r="A17" s="6">
+      <x:c r="A17" s="4">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C17" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D17" s="2">
         <x:v>35</x:v>
@@ -1282,7 +1304,7 @@
       <x:c r="F17" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="11">
+      <x:c r="G17" s="8">
         <x:v>4</x:v>
       </x:c>
       <x:c r="H17" s="3">
@@ -1297,7 +1319,7 @@
     <x:mergeCell ref="A15:F15"/>
     <x:mergeCell ref="G15:H15"/>
   </x:mergeCells>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51166665554046630859" footer="0.51166665554046630859"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -1315,43 +1337,43 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:11" ht="44.25" customHeight="1">
-      <x:c r="A1" s="5" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
-      <x:c r="J1" s="4" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1" s="4"/>
+      <x:c r="A1" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B1" s="10"/>
+      <x:c r="C1" s="10"/>
+      <x:c r="D1" s="10"/>
+      <x:c r="E1" s="10"/>
+      <x:c r="F1" s="10"/>
+      <x:c r="J1" s="14" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K1" s="14"/>
     </x:row>
     <x:row r="2" spans="1:11">
       <x:c r="A2" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J2" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J2" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
@@ -1359,10 +1381,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D3" s="2">
         <x:v>22</x:v>
@@ -1373,7 +1395,7 @@
       <x:c r="F3" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J3" s="7">
+      <x:c r="J3" s="5">
         <x:v>2</x:v>
       </x:c>
       <x:c r="K3" s="1">
@@ -1381,14 +1403,14 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
-      <x:c r="A4" s="6">
+      <x:c r="A4" s="4">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D4" s="2">
         <x:v>38</x:v>
@@ -1399,7 +1421,7 @@
       <x:c r="F4" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J4" s="7">
+      <x:c r="J4" s="5">
         <x:v>4</x:v>
       </x:c>
       <x:c r="K4" s="1">
@@ -1411,10 +1433,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D5" s="2">
         <x:v>26</x:v>
@@ -1433,14 +1455,14 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
-      <x:c r="A6" s="6">
+      <x:c r="A6" s="4">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="2">
         <x:v>35</x:v>
@@ -1463,10 +1485,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D7" s="2">
         <x:v>35</x:v>
@@ -1528,30 +1550,35 @@
       <x:c r="J13" s="1"/>
       <x:c r="K13" s="1"/>
     </x:row>
+    <x:row r="14" spans="2:2">
+      <x:c r="B14" s="16" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
     <x:row r="15" spans="1:8">
       <x:c r="A15" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B15" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C15" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B15" s="3" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C15" s="3" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E15" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F15" s="3" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G15" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G15" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="H15" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:8">
@@ -1559,10 +1586,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C16" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D16" s="2">
         <x:v>22</x:v>
@@ -1574,21 +1601,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G16" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H16" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:8">
-      <x:c r="A17" s="6">
+      <x:c r="A17" s="4">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C17" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D17" s="2">
         <x:v>38</x:v>
@@ -1599,7 +1626,7 @@
       <x:c r="F17" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="11">
+      <x:c r="G17" s="8">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H17" s="3">
@@ -1611,10 +1638,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B18" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C18" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D18" s="2">
         <x:v>26</x:v>
@@ -1626,21 +1653,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G18" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H18" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:8">
-      <x:c r="A19" s="6">
+      <x:c r="A19" s="4">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B19" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C19" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D19" s="2">
         <x:v>35</x:v>
@@ -1651,7 +1678,7 @@
       <x:c r="F19" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="11">
+      <x:c r="G19" s="8">
         <x:v>4</x:v>
       </x:c>
       <x:c r="H19" s="3">
@@ -1663,10 +1690,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C20" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D20" s="2">
         <x:v>35</x:v>
@@ -1677,11 +1704,11 @@
       <x:c r="F20" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G20" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H20" t="s">
-        <x:v>3</x:v>
+      <x:c r="G20" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H20" s="9" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1689,7 +1716,7 @@
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="J1:K1"/>
   </x:mergeCells>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51166665554046630859" footer="0.51166665554046630859"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -1707,43 +1734,43 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:11" ht="44.25" customHeight="1">
-      <x:c r="A1" s="5" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
-      <x:c r="J1" s="4" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1" s="4"/>
+      <x:c r="A1" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B1" s="10"/>
+      <x:c r="C1" s="10"/>
+      <x:c r="D1" s="10"/>
+      <x:c r="E1" s="10"/>
+      <x:c r="F1" s="10"/>
+      <x:c r="J1" s="14" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K1" s="14"/>
     </x:row>
     <x:row r="2" spans="1:11">
       <x:c r="A2" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J2" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J2" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
@@ -1751,10 +1778,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D3" s="2">
         <x:v>22</x:v>
@@ -1765,7 +1792,7 @@
       <x:c r="F3" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J3" s="7">
+      <x:c r="J3" s="5">
         <x:v>2</x:v>
       </x:c>
       <x:c r="K3" s="1">
@@ -1773,14 +1800,14 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
-      <x:c r="A4" s="6">
+      <x:c r="A4" s="4">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D4" s="2">
         <x:v>38</x:v>
@@ -1791,7 +1818,7 @@
       <x:c r="F4" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J4" s="7">
+      <x:c r="J4" s="5">
         <x:v>4</x:v>
       </x:c>
       <x:c r="K4" s="1">
@@ -1803,10 +1830,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D5" s="2">
         <x:v>26</x:v>
@@ -1825,14 +1852,14 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
-      <x:c r="A6" s="6">
+      <x:c r="A6" s="4">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="2">
         <x:v>35</x:v>
@@ -1855,10 +1882,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D7" s="2">
         <x:v>35</x:v>
@@ -1916,27 +1943,30 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="10:11">
+    <x:row r="13" spans="2:11">
+      <x:c r="B13" t="s">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="J13" s="1"/>
       <x:c r="K13" s="1"/>
     </x:row>
     <x:row r="14" spans="7:8">
       <x:c r="G14" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H14" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:8">
-      <x:c r="A15" s="6">
+      <x:c r="A15" s="4">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D15" s="2">
         <x:v>38</x:v>
@@ -1947,7 +1977,7 @@
       <x:c r="F15" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="11">
+      <x:c r="G15" s="8">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H15" s="3">
@@ -1955,14 +1985,14 @@
       </x:c>
     </x:row>
     <x:row r="16" spans="1:8">
-      <x:c r="A16" s="6">
+      <x:c r="A16" s="4">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C16" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D16" s="2">
         <x:v>35</x:v>
@@ -1973,7 +2003,7 @@
       <x:c r="F16" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="11">
+      <x:c r="G16" s="8">
         <x:v>4</x:v>
       </x:c>
       <x:c r="H16" s="3">
@@ -1982,22 +2012,22 @@
     </x:row>
     <x:row r="17" spans="1:8">
       <x:c r="A17" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B17" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B17" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C17" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D17" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E17" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F17" s="9" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G17" s="3">
         <x:v>6</x:v>
@@ -2008,22 +2038,22 @@
     </x:row>
     <x:row r="18" spans="1:8">
       <x:c r="A18" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B18" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D18" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B18" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C18" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D18" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E18" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F18" s="9" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G18" s="3">
         <x:v>7</x:v>
@@ -2034,22 +2064,22 @@
     </x:row>
     <x:row r="19" spans="1:8">
       <x:c r="A19" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B19" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D19" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B19" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C19" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D19" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E19" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F19" s="9" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G19" s="3">
         <x:v>8</x:v>
@@ -2060,22 +2090,22 @@
     </x:row>
     <x:row r="20" spans="1:8">
       <x:c r="A20" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B20" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D20" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B20" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C20" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D20" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E20" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F20" s="9" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G20" s="3">
         <x:v>9</x:v>
@@ -2086,22 +2116,22 @@
     </x:row>
     <x:row r="21" spans="1:8">
       <x:c r="A21" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B21" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D21" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B21" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C21" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D21" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E21" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F21" s="9" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G21" s="3">
         <x:v>10</x:v>
@@ -2112,22 +2142,22 @@
     </x:row>
     <x:row r="22" spans="1:8">
       <x:c r="A22" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B22" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D22" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B22" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C22" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D22" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E22" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F22" s="9" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G22" s="3">
         <x:v>11</x:v>
@@ -2138,22 +2168,22 @@
     </x:row>
     <x:row r="23" spans="1:8">
       <x:c r="A23" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B23" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D23" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B23" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C23" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D23" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E23" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F23" s="9" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G23" s="3">
         <x:v>12</x:v>
@@ -2164,22 +2194,22 @@
     </x:row>
     <x:row r="24" spans="1:8">
       <x:c r="A24" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B24" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D24" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B24" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C24" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D24" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E24" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F24" s="9" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G24" s="3">
         <x:v>13</x:v>
@@ -2193,7 +2223,7 @@
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="J1:K1"/>
   </x:mergeCells>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51166665554046630859" footer="0.51166665554046630859"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -2215,48 +2245,48 @@
   <x:sheetData>
     <x:row r="1" spans="1:11">
       <x:c r="A1" s="12" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B1" s="12"/>
       <x:c r="C1" s="12"/>
       <x:c r="D1" s="12"/>
       <x:c r="E1" s="12"/>
       <x:c r="F1" s="12"/>
-      <x:c r="G1" s="14"/>
-      <x:c r="H1" s="14"/>
-      <x:c r="I1" s="14"/>
+      <x:c r="G1" s="9"/>
+      <x:c r="H1" s="9"/>
+      <x:c r="I1" s="9"/>
       <x:c r="J1" s="15" t="s">
-        <x:v>1</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K1" s="15"/>
     </x:row>
     <x:row r="2" spans="1:11">
       <x:c r="A2" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B2" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C2" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B2" s="3" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C2" s="3" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G2" s="9"/>
+      <x:c r="H2" s="9"/>
+      <x:c r="I2" s="9"/>
+      <x:c r="J2" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G2" s="14"/>
-      <x:c r="H2" s="14"/>
-      <x:c r="I2" s="14"/>
-      <x:c r="J2" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="K2" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
@@ -2264,10 +2294,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D3" s="2">
         <x:v>22</x:v>
@@ -2278,10 +2308,10 @@
       <x:c r="F3" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G3" s="14"/>
-      <x:c r="H3" s="14"/>
-      <x:c r="I3" s="14"/>
-      <x:c r="J3" s="11">
+      <x:c r="G3" s="9"/>
+      <x:c r="H3" s="9"/>
+      <x:c r="I3" s="9"/>
+      <x:c r="J3" s="8">
         <x:v>2</x:v>
       </x:c>
       <x:c r="K3" s="3">
@@ -2289,14 +2319,14 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
-      <x:c r="A4" s="6">
+      <x:c r="A4" s="4">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D4" s="2">
         <x:v>38</x:v>
@@ -2307,10 +2337,10 @@
       <x:c r="F4" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G4" s="14"/>
-      <x:c r="H4" s="14"/>
-      <x:c r="I4" s="14"/>
-      <x:c r="J4" s="11">
+      <x:c r="G4" s="9"/>
+      <x:c r="H4" s="9"/>
+      <x:c r="I4" s="9"/>
+      <x:c r="J4" s="8">
         <x:v>4</x:v>
       </x:c>
       <x:c r="K4" s="3">
@@ -2322,10 +2352,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D5" s="2">
         <x:v>26</x:v>
@@ -2336,9 +2366,9 @@
       <x:c r="F5" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G5" s="14"/>
-      <x:c r="H5" s="14"/>
-      <x:c r="I5" s="14"/>
+      <x:c r="G5" s="9"/>
+      <x:c r="H5" s="9"/>
+      <x:c r="I5" s="9"/>
       <x:c r="J5" s="3">
         <x:v>6</x:v>
       </x:c>
@@ -2347,14 +2377,14 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
-      <x:c r="A6" s="6">
+      <x:c r="A6" s="4">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="2">
         <x:v>35</x:v>
@@ -2365,9 +2395,9 @@
       <x:c r="F6" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G6" s="14"/>
-      <x:c r="H6" s="14"/>
-      <x:c r="I6" s="14"/>
+      <x:c r="G6" s="9"/>
+      <x:c r="H6" s="9"/>
+      <x:c r="I6" s="9"/>
       <x:c r="J6" s="3">
         <x:v>7</x:v>
       </x:c>
@@ -2380,10 +2410,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D7" s="2">
         <x:v>35</x:v>
@@ -2394,9 +2424,9 @@
       <x:c r="F7" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G7" s="14"/>
-      <x:c r="H7" s="14"/>
-      <x:c r="I7" s="14"/>
+      <x:c r="G7" s="9"/>
+      <x:c r="H7" s="9"/>
+      <x:c r="I7" s="9"/>
       <x:c r="J7" s="3">
         <x:v>8</x:v>
       </x:c>
@@ -2405,15 +2435,15 @@
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
-      <x:c r="A8" s="14"/>
-      <x:c r="B8" s="14"/>
-      <x:c r="C8" s="14"/>
-      <x:c r="D8" s="14"/>
-      <x:c r="E8" s="14"/>
-      <x:c r="F8" s="14"/>
-      <x:c r="G8" s="14"/>
-      <x:c r="H8" s="14"/>
-      <x:c r="I8" s="14"/>
+      <x:c r="A8" s="9"/>
+      <x:c r="B8" s="9"/>
+      <x:c r="C8" s="9"/>
+      <x:c r="D8" s="9"/>
+      <x:c r="E8" s="9"/>
+      <x:c r="F8" s="9"/>
+      <x:c r="G8" s="9"/>
+      <x:c r="H8" s="9"/>
+      <x:c r="I8" s="9"/>
       <x:c r="J8" s="3">
         <x:v>9</x:v>
       </x:c>
@@ -2422,15 +2452,15 @@
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
-      <x:c r="A9" s="14"/>
-      <x:c r="B9" s="14"/>
-      <x:c r="C9" s="14"/>
-      <x:c r="D9" s="14"/>
-      <x:c r="E9" s="14"/>
-      <x:c r="F9" s="14"/>
-      <x:c r="G9" s="14"/>
-      <x:c r="H9" s="14"/>
-      <x:c r="I9" s="14"/>
+      <x:c r="A9" s="9"/>
+      <x:c r="B9" s="9"/>
+      <x:c r="C9" s="9"/>
+      <x:c r="D9" s="9"/>
+      <x:c r="E9" s="9"/>
+      <x:c r="F9" s="9"/>
+      <x:c r="G9" s="9"/>
+      <x:c r="H9" s="9"/>
+      <x:c r="I9" s="9"/>
       <x:c r="J9" s="3">
         <x:v>10</x:v>
       </x:c>
@@ -2439,15 +2469,15 @@
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
-      <x:c r="A10" s="14"/>
-      <x:c r="B10" s="14"/>
-      <x:c r="C10" s="14"/>
-      <x:c r="D10" s="14"/>
-      <x:c r="E10" s="14"/>
-      <x:c r="F10" s="14"/>
-      <x:c r="G10" s="14"/>
-      <x:c r="H10" s="14"/>
-      <x:c r="I10" s="14"/>
+      <x:c r="A10" s="9"/>
+      <x:c r="B10" s="9"/>
+      <x:c r="C10" s="9"/>
+      <x:c r="D10" s="9"/>
+      <x:c r="E10" s="9"/>
+      <x:c r="F10" s="9"/>
+      <x:c r="G10" s="9"/>
+      <x:c r="H10" s="9"/>
+      <x:c r="I10" s="9"/>
       <x:c r="J10" s="3">
         <x:v>11</x:v>
       </x:c>
@@ -2456,15 +2486,15 @@
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
-      <x:c r="A11" s="14"/>
-      <x:c r="B11" s="14"/>
-      <x:c r="C11" s="14"/>
-      <x:c r="D11" s="14"/>
-      <x:c r="E11" s="14"/>
-      <x:c r="F11" s="14"/>
-      <x:c r="G11" s="14"/>
-      <x:c r="H11" s="14"/>
-      <x:c r="I11" s="14"/>
+      <x:c r="A11" s="9"/>
+      <x:c r="B11" s="9"/>
+      <x:c r="C11" s="9"/>
+      <x:c r="D11" s="9"/>
+      <x:c r="E11" s="9"/>
+      <x:c r="F11" s="9"/>
+      <x:c r="G11" s="9"/>
+      <x:c r="H11" s="9"/>
+      <x:c r="I11" s="9"/>
       <x:c r="J11" s="3">
         <x:v>12</x:v>
       </x:c>
@@ -2473,15 +2503,15 @@
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
-      <x:c r="A12" s="14"/>
-      <x:c r="B12" s="14"/>
-      <x:c r="C12" s="14"/>
-      <x:c r="D12" s="14"/>
-      <x:c r="E12" s="14"/>
-      <x:c r="F12" s="14"/>
-      <x:c r="G12" s="14"/>
-      <x:c r="H12" s="14"/>
-      <x:c r="I12" s="14"/>
+      <x:c r="A12" s="9"/>
+      <x:c r="B12" s="9"/>
+      <x:c r="C12" s="9"/>
+      <x:c r="D12" s="9"/>
+      <x:c r="E12" s="9"/>
+      <x:c r="F12" s="9"/>
+      <x:c r="G12" s="9"/>
+      <x:c r="H12" s="9"/>
+      <x:c r="I12" s="9"/>
       <x:c r="J12" s="3">
         <x:v>13</x:v>
       </x:c>
@@ -2491,28 +2521,28 @@
     </x:row>
     <x:row r="13" spans="1:8">
       <x:c r="A13" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B13" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B13" s="3" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C13" s="3" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E13" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F13" s="3" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G13" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G13" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="H13" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:8">
@@ -2520,10 +2550,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C14" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D14" s="2">
         <x:v>22</x:v>
@@ -2535,21 +2565,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G14" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H14" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:8">
-      <x:c r="A15" s="6">
+      <x:c r="A15" s="4">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D15" s="2">
         <x:v>38</x:v>
@@ -2560,7 +2590,7 @@
       <x:c r="F15" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="11">
+      <x:c r="G15" s="8">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H15" s="3">
@@ -2572,10 +2602,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C16" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D16" s="2">
         <x:v>26</x:v>
@@ -2586,22 +2616,22 @@
       <x:c r="F16" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H16" s="14" t="s">
-        <x:v>3</x:v>
+      <x:c r="G16" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H16" s="9" t="s">
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:8">
-      <x:c r="A17" s="6">
+      <x:c r="A17" s="4">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C17" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D17" s="2">
         <x:v>35</x:v>
@@ -2612,7 +2642,7 @@
       <x:c r="F17" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="11">
+      <x:c r="G17" s="8">
         <x:v>4</x:v>
       </x:c>
       <x:c r="H17" s="3">
@@ -2624,10 +2654,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B18" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C18" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D18" s="2">
         <x:v>35</x:v>
@@ -2638,31 +2668,31 @@
       <x:c r="F18" s="2">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H18" s="14" t="s">
-        <x:v>3</x:v>
+      <x:c r="G18" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H18" s="9" t="s">
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:8">
-      <x:c r="A19" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B19" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D19" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>3</x:v>
+      <x:c r="A19" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B19" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C19" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D19" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E19" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F19" s="9" t="s">
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G19" s="3">
         <x:v>6</x:v>
@@ -2672,23 +2702,23 @@
       </x:c>
     </x:row>
     <x:row r="20" spans="1:8">
-      <x:c r="A20" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B20" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D20" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>3</x:v>
+      <x:c r="A20" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B20" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C20" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D20" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E20" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F20" s="9" t="s">
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G20" s="3">
         <x:v>7</x:v>
@@ -2698,23 +2728,23 @@
       </x:c>
     </x:row>
     <x:row r="21" spans="1:8">
-      <x:c r="A21" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B21" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D21" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>3</x:v>
+      <x:c r="A21" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B21" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C21" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D21" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E21" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F21" s="9" t="s">
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G21" s="3">
         <x:v>8</x:v>
@@ -2724,23 +2754,23 @@
       </x:c>
     </x:row>
     <x:row r="22" spans="1:8">
-      <x:c r="A22" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B22" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D22" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>3</x:v>
+      <x:c r="A22" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B22" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C22" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D22" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E22" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F22" s="9" t="s">
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G22" s="3">
         <x:v>9</x:v>
@@ -2750,23 +2780,23 @@
       </x:c>
     </x:row>
     <x:row r="23" spans="1:8">
-      <x:c r="A23" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B23" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D23" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>3</x:v>
+      <x:c r="A23" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B23" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C23" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D23" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E23" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F23" s="9" t="s">
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G23" s="3">
         <x:v>10</x:v>
@@ -2776,23 +2806,23 @@
       </x:c>
     </x:row>
     <x:row r="24" spans="1:8">
-      <x:c r="A24" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B24" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D24" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>3</x:v>
+      <x:c r="A24" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B24" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C24" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D24" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E24" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F24" s="9" t="s">
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G24" s="3">
         <x:v>11</x:v>
@@ -2802,23 +2832,23 @@
       </x:c>
     </x:row>
     <x:row r="25" spans="1:8">
-      <x:c r="A25" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B25" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D25" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E25" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="s">
-        <x:v>3</x:v>
+      <x:c r="A25" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B25" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C25" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D25" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E25" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F25" s="9" t="s">
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G25" s="3">
         <x:v>12</x:v>
@@ -2828,23 +2858,23 @@
       </x:c>
     </x:row>
     <x:row r="26" spans="1:8">
-      <x:c r="A26" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B26" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C26" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D26" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E26" s="14" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F26" s="14" t="s">
-        <x:v>3</x:v>
+      <x:c r="A26" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B26" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C26" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D26" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E26" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F26" s="9" t="s">
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G26" s="3">
         <x:v>13</x:v>
@@ -2858,7 +2888,7 @@
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="J1:K1"/>
   </x:mergeCells>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51166665554046630859" footer="0.51166665554046630859"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -2870,21 +2900,21 @@
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
   <x:sheetData>
     <x:row r="1" spans="1:12">
-      <x:c r="A1" s="8"/>
-      <x:c r="B1" s="8"/>
-      <x:c r="C1" s="8"/>
-      <x:c r="D1" s="8"/>
-      <x:c r="E1" s="8"/>
-      <x:c r="F1" s="8"/>
-      <x:c r="G1" s="9"/>
-      <x:c r="H1" s="9"/>
-      <x:c r="I1" s="9"/>
-      <x:c r="J1" s="9"/>
-      <x:c r="K1" s="9"/>
-      <x:c r="L1" s="8"/>
+      <x:c r="A1" s="6"/>
+      <x:c r="B1" s="6"/>
+      <x:c r="C1" s="6"/>
+      <x:c r="D1" s="6"/>
+      <x:c r="E1" s="6"/>
+      <x:c r="F1" s="6"/>
+      <x:c r="G1" s="7"/>
+      <x:c r="H1" s="7"/>
+      <x:c r="I1" s="7"/>
+      <x:c r="J1" s="7"/>
+      <x:c r="K1" s="7"/>
+      <x:c r="L1" s="6"/>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51166665554046630859" footer="0.51166665554046630859"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>